--- a/VerveStacks_MEX/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_MEX/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7BAC4CC-88B7-4018-A1CF-02C7B1DE41DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{09602E2A-7EA4-453E-B2AF-CF2FABFAB534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1762,7 +1762,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3EAC47-F73A-40AC-BA6E-183A893D8BBD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A509C71-1CDB-403A-9777-18C476031C71}">
   <dimension ref="B9:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_MEX/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_MEX/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{216B9B1F-B10A-4C2B-8E0D-4DA9F1A192B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33C91A41-63C4-4F03-9CE3-902BF98AEF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1027,7 +1027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF9C29CC-2F74-4ABD-91CA-4487DC394CB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{310C626B-1C1C-4CD6-B4F5-6E5946E7A332}">
   <dimension ref="B9:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_MEX/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_MEX/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33C91A41-63C4-4F03-9CE3-902BF98AEF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BB0095F-C59D-4F31-8C7A-EBCB89FAD322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1027,7 +1027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{310C626B-1C1C-4CD6-B4F5-6E5946E7A332}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DEE5734-FA7B-43DF-80EB-458ECED6F362}">
   <dimension ref="B9:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
